--- a/list.xlsx
+++ b/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m5054\Desktop\A_Minh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m5054\git\smov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F612E6C3-B5CD-4091-836B-E271FD843236}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAAC570-6209-4753-AD48-C86871A85E16}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10755" yWindow="6360" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7500" yWindow="6495" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Trị An</t>
   </si>
@@ -81,9 +81,6 @@
     <t>tram_id</t>
   </si>
   <si>
-    <t>S5CBO00</t>
-  </si>
-  <si>
     <t>Đại Ninh</t>
   </si>
   <si>
@@ -118,6 +115,24 @@
   </si>
   <si>
     <t>51_4</t>
+  </si>
+  <si>
+    <t>Đa Mi</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Đa Nhim</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>48</t>
   </si>
 </sst>
 </file>
@@ -159,7 +174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +188,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="10.375" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
@@ -524,16 +540,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
@@ -544,18 +560,18 @@
         <v>1</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
@@ -569,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -599,19 +615,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -619,24 +635,24 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -644,42 +660,92 @@
         <v>1</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>2</v>
-      </c>
-      <c r="C8" s="3">
-        <v>63</v>
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>63</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>18</v>
+      <c r="J10" s="5">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C3:C4 I3:I4 C6:C7" numberStoredAsText="1"/>
+    <ignoredError sqref="C3:C4 I3:I4 C8:C9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/list.xlsx
+++ b/list.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m5054\git\smov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAAC570-6209-4753-AD48-C86871A85E16}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD651ED-F9E9-49C2-B0BA-1E99EE92B949}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7500" yWindow="6495" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Nhà máy" sheetId="1" r:id="rId1"/>
+    <sheet name="Dầu" sheetId="4" r:id="rId2"/>
+    <sheet name="Bán lại" sheetId="5" r:id="rId3"/>
+    <sheet name="Gió" sheetId="6" r:id="rId4"/>
+    <sheet name="Trạm" sheetId="2" r:id="rId5"/>
+    <sheet name="PC" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
   <si>
     <t>Trị An</t>
   </si>
@@ -33,9 +38,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>Thác Mơ</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
@@ -51,9 +53,6 @@
     <t>size</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>500kV Cầu Bông</t>
   </si>
   <si>
@@ -63,12 +62,6 @@
     <t>num_of_ele</t>
   </si>
   <si>
-    <t>a_id</t>
-  </si>
-  <si>
-    <t>num_of_a</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -126,13 +119,268 @@
     <t>50</t>
   </si>
   <si>
-    <t>Đa Nhim</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
-    <t>48</t>
+    <t>Thác Mơ &amp; Thác Mơ MR</t>
+  </si>
+  <si>
+    <t>Cần Đơn</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Đam Bri</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>Đồng Nai 2</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Srok Phu Miêng</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>Đa Dâng 2</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Bắc Bình</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>48;312</t>
+  </si>
+  <si>
+    <t>Vĩnh Tân 2</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Duyên Hải 1</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Ô Môn</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Phú Mỹ 1</t>
+  </si>
+  <si>
+    <t>BK</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Phú Mỹ 21</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Cà Mau 1</t>
+  </si>
+  <si>
+    <t>BO</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Cà Mau 2</t>
+  </si>
+  <si>
+    <t>BQ</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Nhơn Trạch 1</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Nhơn Trạch 2</t>
+  </si>
+  <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Bà Rịa</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Đa Nhim &amp; Đa Nhim MR</t>
+  </si>
+  <si>
+    <t>MT Bách Khoa Á Châu</t>
+  </si>
+  <si>
+    <t>CQ</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>MT BIM</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>MT Bầu Zôn</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>MT Hậu Giang</t>
+  </si>
+  <si>
+    <t>CW</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>MT Hồ Gia Hoét (GĐ1)</t>
+  </si>
+  <si>
+    <t>CY</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>MT Hồ Tầm Bó</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>MT Phan Lâm</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>MT Phước Hữu Điện Lực 1</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>MT Trí Việt 1</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>MT Tuy Phong</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>MT Vĩnh Hảo</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>MT VSP Binh Thuận II</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>385</t>
   </si>
 </sst>
 </file>
@@ -174,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +437,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,282 +724,927 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="10.375" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="1"/>
-    <col min="3" max="4" width="10.375" style="4"/>
-    <col min="5" max="8" width="10.375" style="1"/>
-    <col min="9" max="9" width="13.375" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="10.375" style="1"/>
+    <col min="1" max="1" width="32.875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.375" style="4"/>
+    <col min="4" max="4" width="10.375" style="1"/>
+    <col min="5" max="5" width="13.375" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="10.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="B2" s="6">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="6">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="6">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="7">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="7">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="7">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
-        <v>2</v>
-      </c>
-      <c r="I5" s="3" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="7">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="7">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="7">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="7">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="5">
-        <v>27</v>
-      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="7">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="7">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="7">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="7">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="7">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="7">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="7">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="7">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="7">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="7">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="7">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="7">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="7">
+        <v>7</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="7">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="7">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="7">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="7">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="7"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="7"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="7"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="7"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="7"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="7"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="7"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="7"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="7"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="7"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="7"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="7"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="7"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="7"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="7"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="7"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="7"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B58" s="7"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B59" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C3:C4 I3:I4 C8:C9" numberStoredAsText="1"/>
+    <ignoredError sqref="B3:B4 E3:E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1D234B-2054-480C-86DC-36D31A4E4921}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="20.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="7">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B718D45-102F-4737-9CFE-4C487308E98D}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8DD2961-D191-4ED1-81E7-1D1C52756440}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F4EF76-A363-45F3-B60A-4C5B32FF1A57}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.375" style="4"/>
+    <col min="4" max="5" width="10.375" style="1"/>
+    <col min="6" max="6" width="13.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>63</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873A3BC6-D927-4CD1-B016-8FC2F537C104}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.375" style="4"/>
+    <col min="4" max="5" width="10.375" style="1"/>
+    <col min="6" max="6" width="13.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>